--- a/nriss-patch-2/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T15:04:42+00:00</t>
+    <t>2026-04-22T16:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T16:14:13+00:00</t>
+    <t>2026-04-22T16:17:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T16:17:14+00:00</t>
+    <t>2026-05-27T14:01:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:01:46+00:00</t>
+    <t>2026-05-27T14:12:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
